--- a/outputs/inventario-materia-prima-excel/inventario-materia-prima-2026-09.xlsx
+++ b/outputs/inventario-materia-prima-excel/inventario-materia-prima-2026-09.xlsx
@@ -10959,10 +10959,10 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:N200"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <autoFilter ref="A4:N200"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -13038,10 +13038,10 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:P35"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <autoFilter ref="A4:P35"/>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
